--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/antofagasta.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M189"/>
+  <dimension ref="A1:M190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1070.81</v>
+        <v>1061.74</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8963.450000000001</v>
+        <v>8887.540000000001</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>747.85</v>
+        <v>740.01</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3276.86</v>
+        <v>3240.35</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2574.68</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>783.16</v>
+        <v>774.4400000000001</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>748.77</v>
+        <v>740.4299999999999</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>755.0599999999999</v>
+        <v>746.65</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3527.97</v>
+        <v>3508.65</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1517.65</v>
+        <v>1515.71</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7134.86</v>
+        <v>7122.2</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2751.62</v>
+        <v>2740.28</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>744.17</v>
+        <v>741.1</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>744.09</v>
+        <v>742.9400000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>960.55</v>
+        <v>959.0599999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7824.21</v>
+        <v>7864.62</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2473.61</v>
+        <v>2486.38</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1602.61</v>
+        <v>1610.89</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1108.83</v>
+        <v>1116.65</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1266.67</v>
+        <v>1275.61</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1323.47</v>
+        <v>1306.36</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5116.76</v>
+        <v>5051.76</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7889.2</v>
+        <v>7788.99</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8126.35</v>
+        <v>8023.13</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>11879.44</v>
+        <v>11728.54</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1365.71</v>
+        <v>1352.12</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>27923.66</v>
+        <v>27823.53</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2217.21</v>
+        <v>2209.26</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4979.58</v>
+        <v>4968.8</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1339.45</v>
+        <v>1336.55</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8719.950000000001</v>
+        <v>8646.09</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3652.52</v>
+        <v>3621.58</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>762.61</v>
+        <v>762</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>10503.99</v>
+        <v>10544.3</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4251.93</v>
+        <v>4271.2</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>986.97</v>
+        <v>991.4400000000001</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>21016.02</v>
+        <v>21111.26</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>11997.67</v>
+        <v>12052.04</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>804.23</v>
+        <v>806.37</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>941.01</v>
+        <v>943.51</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>23683.3</v>
+        <v>23650.08</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1994.58</v>
+        <v>1991.79</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>789.85</v>
+        <v>788.74</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1155.71</v>
+        <v>1157.19</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2731.16</v>
+        <v>2749.95</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1179.18</v>
+        <v>1187.3</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4104.71</v>
+        <v>4139.79</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>5010.21</v>
+        <v>5053.03</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>18281.7</v>
+        <v>18437.94</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2385.85</v>
+        <v>2406.24</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>43268.77</v>
+        <v>43638.53</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1700.19</v>
+        <v>1718.43</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>34498.8</v>
+        <v>34868.86</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>45397.9</v>
+        <v>45955.84</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3142.08</v>
+        <v>3180.69</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>14724.41</v>
+        <v>14804.93</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7917.25</v>
+        <v>7960.55</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>30367.77</v>
+        <v>29930.16</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>8477.77</v>
+        <v>8489.540000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2598.04</v>
+        <v>2589.13</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>792.98</v>
+        <v>788.01</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3944.95</v>
+        <v>3920.23</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>795.62</v>
+        <v>790.64</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3959.82</v>
+        <v>4013.15</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2184.68</v>
+        <v>2214.1</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1232.59</v>
+        <v>1251.35</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>934.72</v>
+        <v>957.45</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>910.1</v>
+        <v>932.23</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1695.55</v>
+        <v>1738.41</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1132.51</v>
+        <v>1166.85</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4586.35</v>
+        <v>4725.42</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2192.3</v>
+        <v>2258.77</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3079.52</v>
+        <v>3172.91</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>979.98</v>
+        <v>1009.7</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>994.29</v>
+        <v>1024.44</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1499.84</v>
+        <v>1544.41</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1556.16</v>
+        <v>1602.41</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3339.64</v>
+        <v>3349.32</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5053.47</v>
+        <v>5079.58</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3716.48</v>
+        <v>3735.68</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>994.37</v>
+        <v>1003.41</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4812</v>
+        <v>4845.5</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1705.81</v>
+        <v>1717.69</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1169.03</v>
+        <v>1176.72</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3612.89</v>
+        <v>3636.68</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1286.48</v>
+        <v>1294.96</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1681.54</v>
+        <v>1696.51</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>6118.82</v>
+        <v>6173.32</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>32932.79</v>
+        <v>32732.68</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1429.62</v>
+        <v>1420.94</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>37025.29</v>
+        <v>36800.31</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>33522.68</v>
+        <v>33393.3</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1199.51</v>
+        <v>1205.72</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>905.13</v>
+        <v>909.8099999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>6707.86</v>
+        <v>6742.58</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>707415-22-CM26</t>
+          <t>2122-31-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6329,17 +6329,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1055.86</v>
+        <v>1026.2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2122-31-CM26</t>
+          <t>707415-22-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6390,17 +6390,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1020.92</v>
+        <v>1061.33</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1076.46</v>
+        <v>1082.03</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>851.98</v>
+        <v>889.6</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2712.56</v>
+        <v>2723.26</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2497.72</v>
+        <v>2507.57</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3279.09</v>
+        <v>3292.02</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>8275.469999999999</v>
+        <v>8411.860000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>4831.54</v>
+        <v>4843.42</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3917.61</v>
+        <v>3927.25</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1774.89</v>
+        <v>1779.26</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2546.99</v>
+        <v>2529.01</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>34827.46</v>
+        <v>34581.68</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>841.02</v>
+        <v>856.27</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>776.8</v>
+        <v>790.89</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>910.01</v>
+        <v>924.26</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1401.77</v>
+        <v>1401.7</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3211.99</v>
+        <v>3225.26</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>20167.36</v>
+        <v>20250.67</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1160.72</v>
+        <v>1165.51</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2174.99</v>
+        <v>2168.99</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3711.26</v>
+        <v>3668.42</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>4394.51</v>
+        <v>4328.97</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1861.78</v>
+        <v>1849.86</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1099.06</v>
+        <v>1083.16</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>17052.35</v>
+        <v>16655.55</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1852.64</v>
+        <v>1793.56</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>951.16</v>
+        <v>920.83</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>780.3200000000001</v>
+        <v>764.9400000000001</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1640.12</v>
+        <v>1596.2</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>791.85</v>
+        <v>770.64</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>812.88</v>
+        <v>791.12</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>821.11</v>
+        <v>823.5</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>886.98</v>
+        <v>889.5599999999999</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1342.4</v>
+        <v>1347.98</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1975.68</v>
+        <v>1983.89</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1597.8</v>
+        <v>1604.44</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1461.81</v>
+        <v>1467.88</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3681.6</v>
+        <v>3675.44</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>780.95</v>
+        <v>779.65</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1011.46</v>
+        <v>1024.92</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>17835.03</v>
+        <v>18037.86</v>
       </c>
     </row>
     <row r="139">
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1451.51</v>
+        <v>1456.07</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1425773-38-CM26</t>
+          <t>707415-56-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>88.951.800-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1557.36</v>
+        <v>4824.44</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>707415-56-CM26</t>
+          <t>1425773-38-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>88.951.800-6</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4804.52</v>
+        <v>1563.82</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>875.3</v>
+        <v>877.12</v>
       </c>
     </row>
     <row r="143">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>822.64</v>
+        <v>817.71</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2258-3439-CM26</t>
+          <t>3845-32-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9196,17 +9196,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>928.14</v>
+        <v>9527.610000000001</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3845-32-CM26</t>
+          <t>2258-3439-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9257,17 +9257,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>9658.93</v>
+        <v>915.52</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1067.19</v>
+        <v>1079.12</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1172.91</v>
+        <v>1186.03</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>4455.9</v>
+        <v>4505.74</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2436.77</v>
+        <v>2455.23</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1135.79</v>
+        <v>1146.59</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>287893.54</v>
+        <v>290038.33</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>10083.46</v>
+        <v>10060.57</v>
       </c>
     </row>
     <row r="153">
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>872.61</v>
+        <v>870.63</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2258-4177-CM26</t>
+          <t>2258-4176-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>99.533.780-0</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9845,13 +9845,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>7325.48</v>
+        <v>2118.78</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2258-4176-CM26</t>
+          <t>2258-4177-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9906,13 +9906,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2124.03</v>
+        <v>7307.39</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3834-143-CM26</t>
+          <t>3858-241-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>COMERCIAL VALLE SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>77.988.165-2</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9967,13 +9967,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>848.3200000000001</v>
+        <v>806.63</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>930-87-CM26</t>
+          <t>3834-143-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9993,17 +9993,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL VALLE SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.988.165-2</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10028,13 +10028,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1250.71</v>
+        <v>851.13</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3858-241-CM26</t>
+          <t>930-87-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10054,17 +10054,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>803.96</v>
+        <v>1254.86</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>963.05</v>
+        <v>968.17</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>7495.92</v>
+        <v>7583.85</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>13119.01</v>
+        <v>13252.42</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2934.61</v>
+        <v>2962.14</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>14382.6</v>
+        <v>14517.5</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>917.77</v>
+        <v>910.8099999999999</v>
       </c>
     </row>
     <row r="165">
@@ -10516,13 +10516,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>4362.37</v>
+        <v>4300.46</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>769-400-CM26</t>
+          <t>769-401-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>7835.08</v>
+        <v>10916.98</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>769-401-CM26</t>
+          <t>3391-381-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>11069.07</v>
+        <v>3186.08</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3391-381-CM26</t>
+          <t>769-400-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>3230.47</v>
+        <v>7727.42</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1094.21</v>
+        <v>1115.01</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>796.39</v>
+        <v>811.53</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2302.72</v>
+        <v>2346.5</v>
       </c>
     </row>
     <row r="172">
@@ -10943,13 +10943,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1171.27</v>
+        <v>1174.89</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>664-32-CM26</t>
+          <t>1233623-309-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10969,17 +10969,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.402.017-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES II REGION</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11004,13 +11004,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>885.4400000000001</v>
+        <v>8464.120000000001</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1573-28-CM26</t>
+          <t>1573-27-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11065,13 +11065,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2524.91</v>
+        <v>33145.34</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1233623-309-CM26</t>
+          <t>664-32-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11091,17 +11091,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.402.017-2</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES II REGION</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11126,13 +11126,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>8486.559999999999</v>
+        <v>883.1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1573-27-CM26</t>
+          <t>1573-28-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>33233.24</v>
+        <v>2518.24</v>
       </c>
     </row>
     <row r="177">
@@ -11248,13 +11248,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1611.06</v>
+        <v>1579.52</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2258-5485-CM26</t>
+          <t>4617-13-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11279,12 +11279,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11294,12 +11294,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11309,13 +11309,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>774.61</v>
+        <v>2169.21</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4617-13-CM26</t>
+          <t>2258-5485-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2148.8</v>
+        <v>781.97</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1222.97</v>
+        <v>1235.27</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>7899.5</v>
+        <v>7978.61</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1260.55</v>
+        <v>1265.46</v>
       </c>
     </row>
     <row r="183">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>4012.55</v>
+        <v>3992.23</v>
       </c>
     </row>
     <row r="184">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>4216.97</v>
+        <v>4244.46</v>
       </c>
     </row>
     <row r="185">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>919.05</v>
+        <v>904.22</v>
       </c>
     </row>
     <row r="186">
@@ -11797,13 +11797,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1017.86</v>
+        <v>1012.22</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3858-338-CM26</t>
+          <t>1233623-389-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11828,12 +11828,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11858,13 +11858,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1358.54</v>
+        <v>23150.66</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1233623-389-CM26</t>
+          <t>3858-338-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>23265.05</v>
+        <v>1351.86</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,68 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>3626.51</v>
+        <v>3650.78</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>650-94-CM26</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>61.814.000-8</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>2201.44</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/antofagasta.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M290"/>
+  <dimension ref="A1:M306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1124,7 +1124,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1346284-117-CM25</t>
+          <t>664-55-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.402.017-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>972.73</v>
+        <v>1569.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1233623-270-CM25</t>
+          <t>1346284-117-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2063.79</v>
+        <v>972.73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>664-55-CM25</t>
+          <t>1233623-269-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.402.017-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1569.44</v>
+        <v>4499.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3391-519-CM25</t>
+          <t>1233623-268-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5314.86</v>
+        <v>18863.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1233623-263-CM25</t>
+          <t>1233623-270-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3340.04</v>
+        <v>2063.79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1233623-262-CM25</t>
+          <t>1233623-263-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>12762.5</v>
+        <v>3340.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1233623-261-CM25</t>
+          <t>1233623-262-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>943.1799999999999</v>
+        <v>12762.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1233623-268-CM25</t>
+          <t>1233623-261-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>18863.59</v>
+        <v>943.1799999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1233623-269-CM25</t>
+          <t>3391-519-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4499.56</v>
+        <v>5314.86</v>
       </c>
     </row>
     <row r="21">
@@ -2222,7 +2222,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3274-167-CM25</t>
+          <t>3858-302-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1562.79</v>
+        <v>2500.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3858-302-CM25</t>
+          <t>2258-19904-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,17 +2303,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2500.08</v>
+        <v>3423.32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2258-19904-CM25</t>
+          <t>3274-167-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3423.32</v>
+        <v>1562.79</v>
       </c>
     </row>
     <row r="33">
@@ -3198,7 +3198,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>697036-68-CM25</t>
+          <t>1057385-366-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3218,17 +3218,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1577.84</v>
+        <v>1341.65</v>
       </c>
     </row>
     <row r="47">
@@ -3320,7 +3320,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057385-366-CM25</t>
+          <t>697036-68-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1341.65</v>
+        <v>1577.84</v>
       </c>
     </row>
     <row r="49">
@@ -3442,7 +3442,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4291-1730-CM25</t>
+          <t>2385-759-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2012.16</v>
+        <v>2050.53</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4291-1733-CM25</t>
+          <t>4291-1730-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>6430.86</v>
+        <v>2012.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2385-759-CM25</t>
+          <t>4291-1733-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2050.53</v>
+        <v>6430.86</v>
       </c>
     </row>
     <row r="53">
@@ -3991,7 +3991,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4291-1995-CM25</t>
+          <t>650-98-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2932.62</v>
+        <v>997.24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>650-98-CM25</t>
+          <t>4291-1982-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>997.24</v>
+        <v>5350.06</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4291-1982-CM25</t>
+          <t>4291-1995-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5350.06</v>
+        <v>2932.62</v>
       </c>
     </row>
     <row r="62">
@@ -4235,7 +4235,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2258-22788-CM25</t>
+          <t>4291-2014-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7307.04</v>
+        <v>16105.58</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2258-22790-CM25</t>
+          <t>2258-22788-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>5380.5</v>
+        <v>7307.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4291-2014-CM25</t>
+          <t>2258-22790-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4377,17 +4377,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>16105.58</v>
+        <v>5380.5</v>
       </c>
     </row>
     <row r="66">
@@ -4727,7 +4727,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1410-1035-CM25</t>
+          <t>2429-2687-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1837.8</v>
+        <v>3842.78</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2429-2687-CM25</t>
+          <t>1410-1035-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4808,17 +4808,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3842.78</v>
+        <v>1837.8</v>
       </c>
     </row>
     <row r="73">
@@ -5337,7 +5337,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2215-1666-CM25</t>
+          <t>1233623-804-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3640.75</v>
+        <v>5360.64</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1233623-804-CM25</t>
+          <t>2215-1666-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5360.64</v>
+        <v>3640.75</v>
       </c>
     </row>
     <row r="83">
@@ -5520,7 +5520,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1573-169-CM25</t>
+          <t>707415-148-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5540,17 +5540,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>8887.540000000001</v>
+        <v>1061.74</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>707415-148-CM25</t>
+          <t>1573-169-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5601,17 +5601,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1061.74</v>
+        <v>8887.540000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5764,7 +5764,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1233623-979-CM25</t>
+          <t>1233623-945-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5819,13 +5819,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>774.4400000000001</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3858-493-CM25</t>
+          <t>1233623-979-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>740.4299999999999</v>
+        <v>774.4400000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5947,7 +5947,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1233623-945-CM25</t>
+          <t>3858-493-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5967,17 +5967,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2546</v>
+        <v>740.4299999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6313,7 +6313,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1346284-209-CM25</t>
+          <t>707415-172-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6333,17 +6333,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6368,13 +6368,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>742.9400000000001</v>
+        <v>959.0599999999999</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>707415-172-CM25</t>
+          <t>1346284-209-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6429,13 +6429,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>959.0599999999999</v>
+        <v>742.9400000000001</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2215-1876-CM25</t>
+          <t>664-80-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.402.017-2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>7864.62</v>
+        <v>1610.89</v>
       </c>
     </row>
     <row r="100">
@@ -6557,7 +6557,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>664-80-CM25</t>
+          <t>2215-1876-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.402.017-2</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES II REGION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1610.89</v>
+        <v>7864.62</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1230848-339-CM25</t>
+          <t>707415-175-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6673,13 +6673,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1116.65</v>
+        <v>1275.61</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>707415-175-CM25</t>
+          <t>1230848-339-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6699,17 +6699,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1275.61</v>
+        <v>1116.65</v>
       </c>
     </row>
     <row r="104">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6801,7 +6801,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1233623-1095-CM25</t>
+          <t>1233623-1107-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>11728.54</v>
+        <v>5051.76</v>
       </c>
     </row>
     <row r="106">
@@ -6923,7 +6923,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1233623-1107-CM25</t>
+          <t>1233623-1095-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>5051.76</v>
+        <v>11728.54</v>
       </c>
     </row>
     <row r="108">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7594,7 +7594,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1233623-1490-CM25</t>
+          <t>1233623-1486-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7649,13 +7649,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>12052.04</v>
+        <v>4271.2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1230848-366-CM25</t>
+          <t>1233623-1490-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7675,17 +7675,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>991.4400000000001</v>
+        <v>12052.04</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1233623-1486-CM25</t>
+          <t>1233623-1440-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>4271.2</v>
+        <v>21111.26</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1233623-1440-CM25</t>
+          <t>1230848-366-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>21111.26</v>
+        <v>991.4400000000001</v>
       </c>
     </row>
     <row r="122">
@@ -8448,7 +8448,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1233623-1499-CM25</t>
+          <t>1233623-1577-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2406.24</v>
+        <v>5053.03</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1233623-1292-CM25</t>
+          <t>1233623-1499-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8564,13 +8564,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>43638.53</v>
+        <v>2406.24</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1233623-1577-CM25</t>
+          <t>1233623-1292-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5053.03</v>
+        <v>43638.53</v>
       </c>
     </row>
     <row r="135">
@@ -8753,7 +8753,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1233623-1616-CM25</t>
+          <t>1445246-27-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8773,17 +8773,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8808,13 +8808,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>45955.84</v>
+        <v>3180.69</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1445246-27-CM25</t>
+          <t>1233623-1616-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8834,17 +8834,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3180.69</v>
+        <v>45955.84</v>
       </c>
     </row>
     <row r="139">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9180,7 +9180,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1113265-4-CM26</t>
+          <t>1113265-3-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9235,13 +9235,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>790.64</v>
+        <v>3920.23</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1113265-5-CM26</t>
+          <t>1113265-4-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>99.533.780-0</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>788.01</v>
+        <v>790.64</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1113265-3-CM26</t>
+          <t>1113265-5-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>3920.23</v>
+        <v>788.01</v>
       </c>
     </row>
     <row r="147">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9546,7 +9546,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1498185-1-CM26</t>
+          <t>1250561-1-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>65.483.190-4</t>
+          <t>65.438.990-K</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>FUND CENTRO CULTURAL PALACIO DE LA MONEDA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9601,13 +9601,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>957.45</v>
+        <v>932.23</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1250561-1-CM26</t>
+          <t>3846-8-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9622,22 +9622,22 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>65.438.990-K</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CET Calama</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9662,13 +9662,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>932.23</v>
+        <v>1738.41</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3846-8-CM26</t>
+          <t>4291-126-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9723,13 +9723,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1738.41</v>
+        <v>1166.85</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>4291-122-CM26</t>
+          <t>3916-42-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9749,17 +9749,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1009.7</v>
+        <v>4725.42</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4291-123-CM26</t>
+          <t>4291-124-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>3172.91</v>
+        <v>1024.44</v>
       </c>
     </row>
     <row r="155">
@@ -9912,7 +9912,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4291-124-CM26</t>
+          <t>4291-123-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9967,13 +9967,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1024.44</v>
+        <v>3172.91</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4291-126-CM26</t>
+          <t>4291-122-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10028,13 +10028,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1166.85</v>
+        <v>1009.7</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3916-42-CM26</t>
+          <t>3846-10-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10049,22 +10049,22 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>4725.42</v>
+        <v>1544.41</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3846-10-CM26</t>
+          <t>4291-132-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10115,17 +10115,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10135,12 +10135,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1544.41</v>
+        <v>1602.41</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4291-132-CM26</t>
+          <t>1775-4-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10166,12 +10166,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10211,13 +10211,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1602.41</v>
+        <v>3349.32</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1775-4-CM26</t>
+          <t>707415-11-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10232,22 +10232,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10272,13 +10272,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3349.32</v>
+        <v>5079.58</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>707415-11-CM26</t>
+          <t>3274-32-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10298,17 +10298,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10333,13 +10333,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>5079.58</v>
+        <v>3735.68</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3274-32-CM26</t>
+          <t>1346284-34-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10394,13 +10394,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3735.68</v>
+        <v>1003.41</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1346284-34-CM26</t>
+          <t>2429-100-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1003.41</v>
+        <v>4845.5</v>
       </c>
     </row>
     <row r="165">
@@ -10522,7 +10522,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2429-100-CM26</t>
+          <t>922070-30-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>65.117.365-5</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>4845.5</v>
+        <v>1176.72</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>922070-30-CM26</t>
+          <t>2122-20-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>65.117.365-5</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Antofagasta</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1176.72</v>
+        <v>3636.68</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2122-20-CM26</t>
+          <t>1410-99-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.067.906-9</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10699,13 +10699,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>3636.68</v>
+        <v>1294.96</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1410-99-CM26</t>
+          <t>650-9-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10745,12 +10745,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10760,13 +10760,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1294.96</v>
+        <v>1696.51</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>650-9-CM26</t>
+          <t>1057384-159-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10821,13 +10821,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1696.51</v>
+        <v>6173.32</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1057384-159-CM26</t>
+          <t>2215-174-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10852,12 +10852,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10882,13 +10882,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>6173.32</v>
+        <v>36800.31</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2215-174-CM26</t>
+          <t>3149-54-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10913,12 +10913,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10943,13 +10943,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>36800.31</v>
+        <v>32732.68</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3149-54-CM26</t>
+          <t>2215-176-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11004,13 +11004,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>32732.68</v>
+        <v>1420.94</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2215-176-CM26</t>
+          <t>558869-26-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11025,22 +11025,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11065,13 +11065,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1420.94</v>
+        <v>33393.3</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>558869-26-CM26</t>
+          <t>707415-21-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11126,13 +11126,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>33393.3</v>
+        <v>1082.03</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3858-84-CM26</t>
+          <t>707415-22-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11187,13 +11187,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1205.72</v>
+        <v>1061.33</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>558869-28-CM26</t>
+          <t>2122-31-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11213,17 +11213,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11248,13 +11248,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>6742.58</v>
+        <v>1026.2</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3858-85-CM26</t>
+          <t>558869-28-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11279,12 +11279,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11294,12 +11294,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11309,13 +11309,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>909.8099999999999</v>
+        <v>6742.58</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>707415-22-CM26</t>
+          <t>3858-84-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1061.33</v>
+        <v>1205.72</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2122-31-CM26</t>
+          <t>3858-85-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11396,17 +11396,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11416,12 +11416,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11431,13 +11431,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1026.2</v>
+        <v>909.8099999999999</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>707415-21-CM26</t>
+          <t>1410-146-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11447,27 +11447,27 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11492,13 +11492,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1082.03</v>
+        <v>889.6</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1410-146-CM26</t>
+          <t>3391-159-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11523,12 +11523,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11553,13 +11553,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>889.6</v>
+        <v>3292.02</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1233623-48-CM26</t>
+          <t>3391-158-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11584,12 +11584,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11599,12 +11599,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11614,13 +11614,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2723.26</v>
+        <v>2507.57</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3391-158-CM26</t>
+          <t>1233623-48-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11660,12 +11660,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2507.57</v>
+        <v>2723.26</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3391-159-CM26</t>
+          <t>1079454-56-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11736,13 +11736,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3292.02</v>
+        <v>8411.860000000001</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1079454-56-CM26</t>
+          <t>3858-97-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11757,22 +11757,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>8411.860000000001</v>
+        <v>4843.42</v>
       </c>
     </row>
     <row r="187">
@@ -11925,7 +11925,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3858-97-CM26</t>
+          <t>769-136-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11940,22 +11940,22 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11980,13 +11980,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>4843.42</v>
+        <v>34581.68</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>769-136-CM26</t>
+          <t>3845-14-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12006,17 +12006,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12041,13 +12041,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>34581.68</v>
+        <v>2529.01</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3845-14-CM26</t>
+          <t>1346284-56-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12062,22 +12062,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12087,12 +12087,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>2529.01</v>
+        <v>856.27</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1346284-56-CM26</t>
+          <t>1410-184-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12133,12 +12133,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12148,12 +12148,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12163,13 +12163,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>856.27</v>
+        <v>790.89</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1410-184-CM26</t>
+          <t>1057385-66-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12224,13 +12224,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>790.89</v>
+        <v>924.26</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1057385-66-CM26</t>
+          <t>4291-180-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12245,22 +12245,22 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12270,12 +12270,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12285,13 +12285,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>924.26</v>
+        <v>1401.7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>4291-180-CM26</t>
+          <t>778998-15-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12306,22 +12306,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12346,13 +12346,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1401.7</v>
+        <v>3225.26</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>697036-11-CM26</t>
+          <t>1079454-67-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12372,17 +12372,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12392,12 +12392,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12407,13 +12407,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1165.51</v>
+        <v>20250.67</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1079454-67-CM26</t>
+          <t>697036-11-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12433,17 +12433,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12453,12 +12453,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12468,13 +12468,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>20250.67</v>
+        <v>1165.51</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>778998-15-CM26</t>
+          <t>4617-7-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12499,12 +12499,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12529,13 +12529,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3225.26</v>
+        <v>2168.99</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4617-7-CM26</t>
+          <t>1077908-54-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12560,12 +12560,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12590,13 +12590,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2168.99</v>
+        <v>3668.42</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1077908-54-CM26</t>
+          <t>1410-236-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12621,12 +12621,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.067.906-9</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12651,13 +12651,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>3668.42</v>
+        <v>4328.97</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1410-236-CM26</t>
+          <t>778998-22-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12682,12 +12682,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12697,12 +12697,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12712,13 +12712,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>4328.97</v>
+        <v>1849.86</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>778998-22-CM26</t>
+          <t>712-11-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12773,13 +12773,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1849.86</v>
+        <v>1083.16</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>712-11-CM26</t>
+          <t>2258-2613-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12804,12 +12804,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12819,12 +12819,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12834,13 +12834,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1083.16</v>
+        <v>16655.55</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2258-2613-CM26</t>
+          <t>3858-140-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12850,27 +12850,27 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12895,13 +12895,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>16655.55</v>
+        <v>1793.56</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3858-140-CM26</t>
+          <t>3858-141-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12941,12 +12941,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12956,13 +12956,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1793.56</v>
+        <v>920.83</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3858-141-CM26</t>
+          <t>3858-147-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13002,12 +13002,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13017,13 +13017,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>920.83</v>
+        <v>764.9400000000001</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3858-147-CM26</t>
+          <t>1077908-64-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13038,22 +13038,22 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13078,13 +13078,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>764.9400000000001</v>
+        <v>1596.2</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1077908-64-CM26</t>
+          <t>3858-158-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13104,17 +13104,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13124,12 +13124,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13139,13 +13139,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1596.2</v>
+        <v>770.64</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3858-158-CM26</t>
+          <t>3858-159-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13185,12 +13185,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13200,13 +13200,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>770.64</v>
+        <v>791.12</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3858-159-CM26</t>
+          <t>662457-6-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13221,22 +13221,22 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13261,13 +13261,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>791.12</v>
+        <v>823.5</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>662457-6-CM26</t>
+          <t>1220203-27-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13292,12 +13292,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Tribunal Oral en Lo Penal Antofagasta</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13307,12 +13307,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13322,13 +13322,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>823.5</v>
+        <v>889.5599999999999</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1220203-27-CM26</t>
+          <t>1410-292-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13368,12 +13368,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13383,13 +13383,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>889.5599999999999</v>
+        <v>1347.98</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>3858-162-CM26</t>
+          <t>3858-163-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13444,13 +13444,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1467.88</v>
+        <v>1983.89</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>3858-163-CM26</t>
+          <t>548850-34-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13470,17 +13470,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13505,13 +13505,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1983.89</v>
+        <v>1604.44</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>548850-34-CM26</t>
+          <t>3858-162-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13531,17 +13531,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13551,12 +13551,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13566,13 +13566,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1604.44</v>
+        <v>1467.88</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1410-292-CM26</t>
+          <t>2258-2940-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -13597,12 +13597,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1347.98</v>
+        <v>3675.44</v>
       </c>
     </row>
     <row r="217">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13694,7 +13694,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2258-2940-CM26</t>
+          <t>1220203-32-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -13719,12 +13719,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>3675.44</v>
+        <v>1024.92</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1220203-32-CM26</t>
+          <t>1354-11-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -13780,12 +13780,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>61.002.008-9</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13795,12 +13795,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13810,13 +13810,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1024.92</v>
+        <v>18037.86</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1354-11-CM26</t>
+          <t>1057385-114-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.002.008-9</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13856,12 +13856,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13871,13 +13871,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>18037.86</v>
+        <v>1456.07</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1057385-114-CM26</t>
+          <t>707415-56-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13892,22 +13892,22 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13932,13 +13932,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1456.07</v>
+        <v>4824.44</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>707415-56-CM26</t>
+          <t>1425773-38-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>88.951.800-6</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -13993,13 +13993,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>4824.44</v>
+        <v>1563.82</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1425773-38-CM26</t>
+          <t>1057385-120-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14014,22 +14014,22 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>88.951.800-6</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14039,12 +14039,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14054,13 +14054,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1563.82</v>
+        <v>877.12</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1057385-120-CM26</t>
+          <t>1346284-91-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14070,12 +14070,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -14085,12 +14085,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14100,12 +14100,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14115,13 +14115,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>877.12</v>
+        <v>817.71</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1346284-91-CM26</t>
+          <t>2258-3439-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -14146,12 +14146,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14161,12 +14161,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14176,13 +14176,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>817.71</v>
+        <v>915.52</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2258-3439-CM26</t>
+          <t>3845-32-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14202,17 +14202,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14222,12 +14222,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14237,13 +14237,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>915.52</v>
+        <v>9527.610000000001</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>3845-32-CM26</t>
+          <t>778992-108-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14258,22 +14258,22 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14283,12 +14283,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>9527.610000000001</v>
+        <v>4505.74</v>
       </c>
     </row>
     <row r="228">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14426,7 +14426,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>778992-108-CM26</t>
+          <t>4291-472-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14441,22 +14441,22 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14466,12 +14466,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14481,13 +14481,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>4505.74</v>
+        <v>2455.23</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>4291-472-CM26</t>
+          <t>2429-506-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14502,22 +14502,22 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14527,12 +14527,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14542,13 +14542,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2455.23</v>
+        <v>1146.59</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2429-506-CM26</t>
+          <t>558869-57-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14563,22 +14563,22 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14588,28 +14588,32 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr"/>
+          <t>76.213.681-3</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1146.59</v>
+        <v>290038.33</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>558869-57-CM26</t>
+          <t>4468-64-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14624,7 +14628,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -14634,12 +14638,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14649,26 +14653,22 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>290038.33</v>
+        <v>10060.57</v>
       </c>
     </row>
     <row r="234">
@@ -14735,7 +14735,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>4468-64-CM26</t>
+          <t>2258-4176-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14750,22 +14750,22 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14775,12 +14775,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>99.533.780-0</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -14790,13 +14790,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>10060.57</v>
+        <v>2118.78</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2258-4176-CM26</t>
+          <t>2258-4177-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14836,12 +14836,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -14851,13 +14851,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>2118.78</v>
+        <v>7307.39</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2258-4177-CM26</t>
+          <t>3834-143-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14872,22 +14872,22 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14897,12 +14897,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL VALLE SPA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.988.165-2</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -14912,13 +14912,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>7307.39</v>
+        <v>851.13</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3834-143-CM26</t>
+          <t>930-87-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14938,17 +14938,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>COMERCIAL VALLE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>77.988.165-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -14973,13 +14973,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>851.13</v>
+        <v>1254.86</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>930-87-CM26</t>
+          <t>3858-241-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14999,17 +14999,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15019,12 +15019,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15034,13 +15034,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1254.86</v>
+        <v>806.63</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3858-241-CM26</t>
+          <t>707415-66-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -15065,12 +15065,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15080,12 +15080,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15095,13 +15095,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>806.63</v>
+        <v>968.17</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>707415-66-CM26</t>
+          <t>3858-249-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15111,12 +15111,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15156,13 +15156,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>968.17</v>
+        <v>7583.85</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>3858-249-CM26</t>
+          <t>1233623-244-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -15187,12 +15187,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15217,13 +15217,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>7583.85</v>
+        <v>13252.42</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1233623-244-CM26</t>
+          <t>1697-149-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15238,22 +15238,22 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15263,12 +15263,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15278,13 +15278,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>13252.42</v>
+        <v>2962.14</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1697-149-CM26</t>
+          <t>2385-399-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15324,12 +15324,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15339,13 +15339,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2962.14</v>
+        <v>14517.5</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2385-399-CM26</t>
+          <t>1253-7-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15360,22 +15360,22 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>60.805.055-8</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15385,12 +15385,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>14517.5</v>
+        <v>910.8099999999999</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1253-7-CM26</t>
+          <t>2215-673-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15421,7 +15421,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>60.805.055-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Tesorería Provincial El Loa - Calama</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -15461,13 +15461,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>910.8099999999999</v>
+        <v>4300.46</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2215-673-CM26</t>
+          <t>769-401-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -15492,12 +15492,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -15522,13 +15522,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>4300.46</v>
+        <v>10916.98</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>769-400-CM26</t>
+          <t>3391-381-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15553,12 +15553,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15568,12 +15568,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -15583,13 +15583,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>7727.42</v>
+        <v>3186.08</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>769-401-CM26</t>
+          <t>769-400-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15644,13 +15644,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>10916.98</v>
+        <v>7727.42</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>3391-381-CM26</t>
+          <t>930-104-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -15675,12 +15675,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15690,12 +15690,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -15705,13 +15705,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>3186.08</v>
+        <v>1115.01</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1057384-508-CM26</t>
+          <t>930-105-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15751,12 +15751,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -15766,13 +15766,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2346.5</v>
+        <v>811.53</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>930-105-CM26</t>
+          <t>1057384-508-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15797,12 +15797,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15812,12 +15812,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -15827,13 +15827,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>811.53</v>
+        <v>2346.5</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>930-104-CM26</t>
+          <t>1410-543-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -15858,12 +15858,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>78.067.906-9</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -15888,13 +15888,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1115.01</v>
+        <v>1174.89</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1410-543-CM26</t>
+          <t>1573-28-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -15919,12 +15919,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15934,12 +15934,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1174.89</v>
+        <v>2518.24</v>
       </c>
     </row>
     <row r="255">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES II REGION</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16138,7 +16138,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1573-28-CM26</t>
+          <t>2258-5255-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16153,22 +16153,22 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16178,12 +16178,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -16193,13 +16193,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2518.24</v>
+        <v>1579.52</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2258-5255-CM26</t>
+          <t>2258-5485-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16209,12 +16209,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16254,13 +16254,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1579.52</v>
+        <v>781.97</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2258-5485-CM26</t>
+          <t>4617-13-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16285,12 +16285,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16300,12 +16300,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -16315,13 +16315,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>781.97</v>
+        <v>2169.21</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>4617-13-CM26</t>
+          <t>778992-188-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -16346,12 +16346,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16361,12 +16361,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16376,13 +16376,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2169.21</v>
+        <v>1235.27</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>778992-188-CM26</t>
+          <t>2258-5199-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -16407,12 +16407,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16437,13 +16437,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1235.27</v>
+        <v>7978.61</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2258-5199-CM26</t>
+          <t>2122-140-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -16468,12 +16468,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16483,12 +16483,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -16498,13 +16498,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>7978.61</v>
+        <v>1265.46</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2122-140-CM26</t>
+          <t>707415-84-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16519,22 +16519,22 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16544,12 +16544,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -16559,13 +16559,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1265.46</v>
+        <v>3992.23</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>707415-84-CM26</t>
+          <t>1077908-129-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16580,22 +16580,22 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16620,13 +16620,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>3992.23</v>
+        <v>4244.46</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1077908-129-CM26</t>
+          <t>1261592-898-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -16651,12 +16651,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16666,12 +16666,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -16681,13 +16681,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>4244.46</v>
+        <v>904.22</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1261592-898-CM26</t>
+          <t>1077908-134-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16702,22 +16702,22 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16727,12 +16727,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -16742,13 +16742,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>904.22</v>
+        <v>1012.22</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1077908-134-CM26</t>
+          <t>3858-338-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16763,22 +16763,22 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16788,12 +16788,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -16803,13 +16803,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1012.22</v>
+        <v>1351.86</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>3858-338-CM26</t>
+          <t>1233623-389-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16834,12 +16834,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16864,13 +16864,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1351.86</v>
+        <v>23150.66</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1233623-389-CM26</t>
+          <t>1233623-401-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16885,7 +16885,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -16925,13 +16925,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>23150.66</v>
+        <v>3650.78</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1233623-401-CM26</t>
+          <t>1346284-145-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16941,27 +16941,27 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -16971,12 +16971,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -16986,13 +16986,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>3650.78</v>
+        <v>906.91</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1346284-145-CM26</t>
+          <t>1346284-148-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -17047,13 +17047,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>906.91</v>
+        <v>1725.26</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1346284-148-CM26</t>
+          <t>1410-728-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17078,12 +17078,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17108,13 +17108,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1725.26</v>
+        <v>796.6900000000001</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1410-728-CM26</t>
+          <t>993-170-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17129,22 +17129,22 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17169,13 +17169,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>796.6900000000001</v>
+        <v>811.91</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>993-170-CM26</t>
+          <t>1233623-490-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17200,12 +17200,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17215,12 +17215,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -17230,13 +17230,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>811.91</v>
+        <v>5440.62</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1233623-490-CM26</t>
+          <t>707415-94-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17261,12 +17261,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17291,13 +17291,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>5440.62</v>
+        <v>1108.56</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>707415-94-CM26</t>
+          <t>650-94-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17312,22 +17312,22 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17352,13 +17352,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>1108.56</v>
+        <v>2201.44</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1233623-453-CM26</t>
+          <t>1697-221-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17383,12 +17383,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17398,12 +17398,12 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>4269.32</v>
+        <v>4785.88</v>
       </c>
     </row>
     <row r="279">
@@ -17480,7 +17480,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1697-221-CM26</t>
+          <t>1233623-453-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17505,12 +17505,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17520,12 +17520,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K280" t="inlineStr"/>
@@ -17535,13 +17535,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>4785.88</v>
+        <v>4269.32</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>650-94-CM26</t>
+          <t>1410-789-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -17566,12 +17566,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17581,12 +17581,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
@@ -17596,13 +17596,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2201.44</v>
+        <v>1224.21</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1410-789-CM26</t>
+          <t>1233623-492-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17617,22 +17617,22 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -17657,13 +17657,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1224.21</v>
+        <v>34033.98</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1233623-492-CM26</t>
+          <t>1033-53-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17683,17 +17683,17 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17718,13 +17718,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>34033.98</v>
+        <v>791.8099999999999</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1033-53-CM26</t>
+          <t>778992-221-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17739,7 +17739,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -17749,12 +17749,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17764,12 +17764,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>791.8099999999999</v>
+        <v>1560.68</v>
       </c>
     </row>
     <row r="285">
@@ -17846,7 +17846,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>778992-221-CM26</t>
+          <t>769-604-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17861,22 +17861,22 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17886,12 +17886,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -17901,7 +17901,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1560.68</v>
+        <v>3126.27</v>
       </c>
     </row>
     <row r="287">
@@ -17968,7 +17968,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>769-604-CM26</t>
+          <t>2258-6907-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -17993,12 +17993,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18008,12 +18008,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K288" t="inlineStr"/>
@@ -18023,13 +18023,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>3126.27</v>
+        <v>4475.76</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2258-6907-CM26</t>
+          <t>1013609-113-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -18054,12 +18054,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>65.158.175-3</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18069,12 +18069,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K289" t="inlineStr"/>
@@ -18084,13 +18084,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>4475.76</v>
+        <v>982.76</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1013609-113-CM26</t>
+          <t>1233623-608-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18100,12 +18100,12 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -18115,12 +18115,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>65.158.175-3</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18130,12 +18130,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -18145,7 +18145,983 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>982.76</v>
+        <v>1982.02</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>1057385-310-CM26</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>61.606.204-2</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="n">
+        <v>1165.41</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>1220203-95-CM26</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>60.905.047-0</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="n">
+        <v>1471.64</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>4999-46-CM26</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>69.252.500-0</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="n">
+        <v>3245.73</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>1233623-676-CM26</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="n">
+        <v>11445.21</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>1261592-1169-CM26</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="n">
+        <v>7444.51</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>1233623-607-CM26</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="n">
+        <v>3677.64</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>1233623-673-CM26</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="n">
+        <v>11609.76</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>697036-66-CM26</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="n">
+        <v>2329.1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>1057385-343-CM26</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>61.606.204-2</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="n">
+        <v>1415.49</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>1233623-752-CM26</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="n">
+        <v>16945.52</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>3916-386-CM26</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>69.020.500-9</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M301" s="2" t="n">
+        <v>3014.78</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>1233623-706-CM26</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="n">
+        <v>16481.24</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>1410-888-CM26</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>61.004.007-1</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="n">
+        <v>1043.97</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>1233623-763-CM26</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="n">
+        <v>4724.86</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>3858-425-CM26</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="n">
+        <v>751.9299999999999</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>3391-573-CM26</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>61.101.086-9</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="n">
+        <v>2571.59</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/antofagasta.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M415"/>
+  <dimension ref="A1:M426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -904,7 +904,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4291-121-CM25</t>
+          <t>2258-5004-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8193.24</v>
+        <v>19532.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4291-122-CM25</t>
+          <t>1057385-28-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1734.5</v>
+        <v>1699.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2258-5004-CM25</t>
+          <t>4291-121-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>19532.01</v>
+        <v>8193.24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057385-28-CM25</t>
+          <t>4291-122-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1699.59</v>
+        <v>1734.5</v>
       </c>
     </row>
     <row r="12">
@@ -1684,7 +1684,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1113265-13-CM25</t>
+          <t>707415-18-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1724,17 +1724,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1425.49</v>
+        <v>4389.21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>707415-18-CM25</t>
+          <t>1113265-12-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4389.21</v>
+        <v>747.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1113265-12-CM25</t>
+          <t>1113265-13-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1854,17 +1854,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>747.29</v>
+        <v>1425.49</v>
       </c>
     </row>
     <row r="23">
@@ -2265,7 +2265,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2215-321-CM25</t>
+          <t>3391-201-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2305,17 +2305,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>13693.91</v>
+        <v>1921.29</v>
       </c>
     </row>
     <row r="30">
@@ -2395,7 +2395,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3391-201-CM25</t>
+          <t>3391-203-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1921.29</v>
+        <v>3700.07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3391-203-CM25</t>
+          <t>2215-321-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3700.07</v>
+        <v>13693.91</v>
       </c>
     </row>
     <row r="33">
@@ -2590,7 +2590,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2122-53-CM25</t>
+          <t>1346284-32-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2630,17 +2630,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2618.81</v>
+        <v>2163.77</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1346284-32-CM25</t>
+          <t>1079454-31-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2714,13 +2714,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2163.77</v>
+        <v>34045.61</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1079454-31-CM25</t>
+          <t>2122-53-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>34045.61</v>
+        <v>2618.81</v>
       </c>
     </row>
     <row r="37">
@@ -2980,7 +2980,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3916-159-CM25</t>
+          <t>1220203-27-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3020,17 +3020,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1791.38</v>
+        <v>737.89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1220203-27-CM25</t>
+          <t>3916-159-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3085,17 +3085,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>737.89</v>
+        <v>1791.38</v>
       </c>
     </row>
     <row r="42">
@@ -3370,7 +3370,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1079454-107-CM25</t>
+          <t>3149-102-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3410,28 +3410,32 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2634.28</v>
+        <v>5625.48</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3149-102-CM25</t>
+          <t>1079454-107-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3456,12 +3460,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3471,32 +3475,28 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5625.48</v>
+        <v>2634.28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>697036-20-CM25</t>
+          <t>1775-13-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3536,17 +3536,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3555,13 +3555,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1352.22</v>
+        <v>2283.42</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1775-13-CM25</t>
+          <t>697036-20-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2283.42</v>
+        <v>1352.22</v>
       </c>
     </row>
     <row r="50">
@@ -4723,7 +4723,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1057385-173-CM25</t>
+          <t>3858-148-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4763,17 +4763,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>735.99</v>
+        <v>2329.34</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3858-146-CM25</t>
+          <t>1057385-173-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4808,17 +4808,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4828,17 +4828,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4847,13 +4847,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1546.34</v>
+        <v>735.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3858-147-CM25</t>
+          <t>3858-146-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4893,28 +4893,32 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ARTEL S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>92.642.000-3</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>997.52</v>
+        <v>1546.34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3858-148-CM25</t>
+          <t>3858-147-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4934,7 +4938,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4954,26 +4958,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ARTEL S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>92.642.000-3</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2329.34</v>
+        <v>997.52</v>
       </c>
     </row>
     <row r="71">
@@ -5174,7 +5174,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1080164-12-CM25</t>
+          <t>1079454-167-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5233,13 +5233,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1380.38</v>
+        <v>730.28</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>778998-76-CM25</t>
+          <t>1080164-12-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5279,17 +5279,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5298,13 +5298,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4195.66</v>
+        <v>1380.38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1079454-167-CM25</t>
+          <t>778998-76-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5344,17 +5344,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5363,13 +5363,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>730.28</v>
+        <v>4195.66</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2429-1982-CM25</t>
+          <t>3858-193-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5389,17 +5389,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3340.27</v>
+        <v>756.6</v>
       </c>
     </row>
     <row r="78">
@@ -5499,7 +5499,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3858-193-CM25</t>
+          <t>2429-1982-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5519,17 +5519,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>756.6</v>
+        <v>3340.27</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3858-206-CM25</t>
+          <t>1057385-209-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5623,13 +5623,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3256.16</v>
+        <v>1824.95</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1057385-209-CM25</t>
+          <t>3858-206-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1824.95</v>
+        <v>3256.16</v>
       </c>
     </row>
     <row r="82">
@@ -5824,7 +5824,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1230848-89-CM25</t>
+          <t>1230848-90-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5864,28 +5864,32 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ARTEL S.A.</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>92.642.000-3</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>76.213.681-3</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>20795.37</v>
+        <v>1180.82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1230848-90-CM25</t>
+          <t>1230848-89-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5925,26 +5929,22 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>ARTEL S.A.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>92.642.000-3</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1180.82</v>
+        <v>20795.37</v>
       </c>
     </row>
     <row r="86">
@@ -6015,7 +6015,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1261592-3546-CM25</t>
+          <t>778998-100-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6074,13 +6074,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1874.85</v>
+        <v>2301.27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>778998-100-CM25</t>
+          <t>1261592-3545-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6120,17 +6120,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2301.27</v>
+        <v>1131.6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1261592-3545-CM25</t>
+          <t>1261592-3546-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6185,17 +6185,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6204,7 +6204,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1131.6</v>
+        <v>1874.85</v>
       </c>
     </row>
     <row r="90">
@@ -6275,7 +6275,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2385-400-CM25</t>
+          <t>1233623-181-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6300,12 +6300,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6334,13 +6334,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>16219.72</v>
+        <v>7598.43</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1233623-181-CM25</t>
+          <t>2385-400-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6399,13 +6399,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>7598.43</v>
+        <v>16219.72</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3916-260-CM25</t>
+          <t>3916-261-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6445,17 +6445,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA ULAP LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.173.807-9</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6464,13 +6464,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>7366.86</v>
+        <v>832.1799999999999</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3916-261-CM25</t>
+          <t>3916-260-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6510,17 +6510,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA ULAP LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>77.173.807-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6529,13 +6529,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>832.1799999999999</v>
+        <v>7366.86</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2385-432-CM25</t>
+          <t>707415-71-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6575,28 +6575,32 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>INVERSIONES CATALUÑA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.961.219-k</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2618.85</v>
+        <v>3357.46</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2385-431-CM25</t>
+          <t>2385-429-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6616,7 +6620,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6636,17 +6640,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6655,13 +6659,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7875.49</v>
+        <v>13887.93</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>707415-71-CM25</t>
+          <t>2385-432-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6686,12 +6690,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6701,32 +6705,28 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>INVERSIONES CATALUÑA SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.961.219-k</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3357.46</v>
+        <v>2618.85</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2385-429-CM25</t>
+          <t>2385-431-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6766,17 +6766,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>13887.93</v>
+        <v>7875.49</v>
       </c>
     </row>
     <row r="99">
@@ -7116,7 +7116,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1697-147-CM25</t>
+          <t>1375735-41-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2808.19</v>
+        <v>6397</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1375735-41-CM25</t>
+          <t>1697-147-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.981.250-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7240,7 +7240,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>6397</v>
+        <v>2808.19</v>
       </c>
     </row>
     <row r="106">
@@ -8221,7 +8221,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1233623-261-CM25</t>
+          <t>664-55-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.402.017-2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>943.1799999999999</v>
+        <v>1569.44</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1233623-262-CM25</t>
+          <t>1233623-270-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8345,13 +8345,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>12762.5</v>
+        <v>2063.79</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1233623-263-CM25</t>
+          <t>1233623-269-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8410,13 +8410,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3340.04</v>
+        <v>4499.56</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1233623-268-CM25</t>
+          <t>1346284-117-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8456,17 +8456,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8475,13 +8475,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>18863.59</v>
+        <v>972.73</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1233623-269-CM25</t>
+          <t>1233623-263-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8540,13 +8540,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>4499.56</v>
+        <v>3340.04</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1233623-270-CM25</t>
+          <t>1233623-262-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8605,13 +8605,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2063.79</v>
+        <v>12762.5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>664-55-CM25</t>
+          <t>1233623-261-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.402.017-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8670,13 +8670,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1569.44</v>
+        <v>943.1799999999999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1346284-117-CM25</t>
+          <t>1233623-268-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8716,17 +8716,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>972.73</v>
+        <v>18863.59</v>
       </c>
     </row>
     <row r="129">
@@ -9391,7 +9391,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2258-19904-CM25</t>
+          <t>3858-302-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9411,17 +9411,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9431,17 +9431,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9450,13 +9450,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3423.32</v>
+        <v>2500.08</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3858-302-CM25</t>
+          <t>3274-167-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9476,17 +9476,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9496,17 +9496,17 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9515,13 +9515,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2500.08</v>
+        <v>1562.79</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3274-167-CM25</t>
+          <t>2258-19904-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1562.79</v>
+        <v>3423.32</v>
       </c>
     </row>
     <row r="142">
@@ -9716,7 +9716,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>561704-65-CM25</t>
+          <t>561704-66-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9756,32 +9756,28 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.955.038-0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>767.55</v>
+        <v>745.75</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>561704-66-CM25</t>
+          <t>561704-65-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9821,22 +9817,26 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.955.038-0</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>745.75</v>
+        <v>767.55</v>
       </c>
     </row>
     <row r="146">
@@ -10423,7 +10423,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>707415-118-CM25</t>
+          <t>697036-68-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10482,13 +10482,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1864.14</v>
+        <v>1577.84</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1057385-366-CM25</t>
+          <t>707415-118-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10508,17 +10508,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10547,13 +10547,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1341.65</v>
+        <v>1864.14</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>697036-68-CM25</t>
+          <t>1057385-366-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10573,17 +10573,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1577.84</v>
+        <v>1341.65</v>
       </c>
     </row>
     <row r="158">
@@ -10683,7 +10683,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4291-1730-CM25</t>
+          <t>2385-759-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10703,17 +10703,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10742,7 +10742,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2012.16</v>
+        <v>2050.53</v>
       </c>
     </row>
     <row r="160">
@@ -10813,7 +10813,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2385-759-CM25</t>
+          <t>4291-1730-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10833,17 +10833,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10872,7 +10872,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>2050.53</v>
+        <v>2012.16</v>
       </c>
     </row>
     <row r="162">
@@ -12694,7 +12694,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1233623-804-CM25</t>
+          <t>2215-1666-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12719,12 +12719,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12753,13 +12753,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>5360.64</v>
+        <v>3640.75</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2215-1666-CM25</t>
+          <t>1233623-804-CM25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12784,12 +12784,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12818,7 +12818,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>3640.75</v>
+        <v>5360.64</v>
       </c>
     </row>
     <row r="192">
@@ -13084,7 +13084,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1233623-942-CM25</t>
+          <t>1233623-945-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13143,13 +13143,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>3240.35</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1233623-945-CM25</t>
+          <t>1233623-979-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13208,13 +13208,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2546</v>
+        <v>774.4400000000001</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1233623-979-CM25</t>
+          <t>3858-493-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13234,17 +13234,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13254,17 +13254,17 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>774.4400000000001</v>
+        <v>740.4299999999999</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3858-493-CM25</t>
+          <t>3858-498-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13319,32 +13319,28 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>740.4299999999999</v>
+        <v>746.65</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3858-498-CM25</t>
+          <t>1233623-942-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13364,17 +13360,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13384,22 +13380,26 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>746.65</v>
+        <v>3240.35</v>
       </c>
     </row>
     <row r="201">
@@ -13600,7 +13600,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1697-308-CM25</t>
+          <t>1697-305-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13640,12 +13640,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -13655,13 +13655,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>741.1</v>
+        <v>2740.28</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1697-305-CM25</t>
+          <t>1697-308-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13701,12 +13701,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -13716,7 +13716,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2740.28</v>
+        <v>741.1</v>
       </c>
     </row>
     <row r="206">
@@ -13852,7 +13852,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2215-1876-CM25</t>
+          <t>2429-2968-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13872,17 +13872,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13892,17 +13892,17 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13911,13 +13911,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>7864.62</v>
+        <v>2486.38</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2429-2968-CM25</t>
+          <t>2215-1876-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13937,17 +13937,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13957,17 +13957,17 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13976,7 +13976,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2486.38</v>
+        <v>7864.62</v>
       </c>
     </row>
     <row r="210">
@@ -14047,7 +14047,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1230848-339-CM25</t>
+          <t>707415-175-CM25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -14067,17 +14067,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -14087,17 +14087,17 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1116.65</v>
+        <v>1275.61</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>707415-175-CM25</t>
+          <t>1230848-339-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14132,17 +14132,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14152,17 +14152,17 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -14171,7 +14171,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1275.61</v>
+        <v>1116.65</v>
       </c>
     </row>
     <row r="213">
@@ -14307,7 +14307,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1233623-1095-CM25</t>
+          <t>1233623-1096-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14366,13 +14366,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>11728.54</v>
+        <v>7788.99</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1233623-1093-CM25</t>
+          <t>1233623-1095-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14431,13 +14431,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>8023.13</v>
+        <v>11728.54</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1233623-1096-CM25</t>
+          <t>1233623-1093-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14496,7 +14496,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>7788.99</v>
+        <v>8023.13</v>
       </c>
     </row>
     <row r="218">
@@ -15148,7 +15148,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1233623-1440-CM25</t>
+          <t>1233623-1486-CM25</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15207,13 +15207,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>21111.26</v>
+        <v>4271.2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1233623-1486-CM25</t>
+          <t>1233623-1440-CM25</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15272,7 +15272,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>4271.2</v>
+        <v>21111.26</v>
       </c>
     </row>
     <row r="230">
@@ -15863,7 +15863,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1233623-1292-CM25</t>
+          <t>1233623-1408-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15903,17 +15903,17 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -15922,7 +15922,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>43638.53</v>
+        <v>18437.94</v>
       </c>
     </row>
     <row r="240">
@@ -16123,7 +16123,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1233623-1408-CM25</t>
+          <t>1233623-1292-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16163,17 +16163,17 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -16182,7 +16182,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>18437.94</v>
+        <v>43638.53</v>
       </c>
     </row>
     <row r="244">
@@ -17281,7 +17281,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>4291-122-CM26</t>
+          <t>3916-42-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17301,17 +17301,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17321,17 +17321,17 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -17340,13 +17340,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1009.7</v>
+        <v>4725.42</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>4291-123-CM26</t>
+          <t>4291-126-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17405,13 +17405,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3172.91</v>
+        <v>1166.85</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3917-4-CM26</t>
+          <t>4291-124-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17431,17 +17431,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17470,13 +17470,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>2258.77</v>
+        <v>1024.44</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>4291-124-CM26</t>
+          <t>4291-123-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17535,13 +17535,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1024.44</v>
+        <v>3172.91</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>4291-126-CM26</t>
+          <t>4291-122-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17600,13 +17600,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1166.85</v>
+        <v>1009.7</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>3916-42-CM26</t>
+          <t>3917-4-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17646,17 +17646,17 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>4725.42</v>
+        <v>2258.77</v>
       </c>
     </row>
     <row r="267">
@@ -18191,7 +18191,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>922070-30-CM26</t>
+          <t>1410-99-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18216,12 +18216,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>65.117.365-5</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18231,17 +18231,17 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.067.906-9</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -18250,7 +18250,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1176.72</v>
+        <v>1294.96</v>
       </c>
     </row>
     <row r="276">
@@ -18321,7 +18321,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1410-99-CM26</t>
+          <t>922070-30-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18346,12 +18346,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>65.117.365-5</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18361,17 +18361,17 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -18380,7 +18380,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>1294.96</v>
+        <v>1176.72</v>
       </c>
     </row>
     <row r="278">
@@ -18516,7 +18516,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>3149-54-CM26</t>
+          <t>2215-174-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18541,12 +18541,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18575,7 +18575,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>32732.68</v>
+        <v>36800.31</v>
       </c>
     </row>
     <row r="281">
@@ -18646,7 +18646,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2215-174-CM26</t>
+          <t>3149-54-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18671,12 +18671,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18705,7 +18705,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>36800.31</v>
+        <v>32732.68</v>
       </c>
     </row>
     <row r="283">
@@ -18776,7 +18776,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>707415-21-CM26</t>
+          <t>3858-85-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18801,12 +18801,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18816,17 +18816,17 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -18835,13 +18835,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1082.03</v>
+        <v>909.8099999999999</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>707415-22-CM26</t>
+          <t>3858-84-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18866,12 +18866,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18900,13 +18900,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>1061.33</v>
+        <v>1205.72</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2122-31-CM26</t>
+          <t>558869-28-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18926,17 +18926,17 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18946,17 +18946,17 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -18965,13 +18965,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1026.2</v>
+        <v>6742.58</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>558869-28-CM26</t>
+          <t>2122-31-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18991,17 +18991,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19011,17 +19011,17 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -19030,13 +19030,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>6742.58</v>
+        <v>1026.2</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>3858-84-CM26</t>
+          <t>707415-22-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19061,12 +19061,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19095,13 +19095,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1205.72</v>
+        <v>1061.33</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>3858-85-CM26</t>
+          <t>707415-21-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19126,12 +19126,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -19141,17 +19141,17 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -19160,7 +19160,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>909.8099999999999</v>
+        <v>1082.03</v>
       </c>
     </row>
     <row r="290">
@@ -19231,7 +19231,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>3391-159-CM26</t>
+          <t>1233623-48-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19256,12 +19256,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19290,13 +19290,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>3292.02</v>
+        <v>2723.26</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1233623-48-CM26</t>
+          <t>3391-159-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19321,12 +19321,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19355,7 +19355,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>2723.26</v>
+        <v>3292.02</v>
       </c>
     </row>
     <row r="293">
@@ -19556,7 +19556,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>3858-98-CM26</t>
+          <t>3858-99-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19596,17 +19596,17 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>OPEN SANTIAGO SPA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.069.505-6</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -19615,13 +19615,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>3927.25</v>
+        <v>1779.26</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3858-99-CM26</t>
+          <t>3858-98-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19661,17 +19661,17 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>OPEN SANTIAGO SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>78.069.505-6</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1779.26</v>
+        <v>3927.25</v>
       </c>
     </row>
     <row r="298">
@@ -20076,7 +20076,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>778998-15-CM26</t>
+          <t>697036-11-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20096,17 +20096,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -20135,7 +20135,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>3225.26</v>
+        <v>1165.51</v>
       </c>
     </row>
     <row r="305">
@@ -20206,7 +20206,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>697036-11-CM26</t>
+          <t>778998-15-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20226,17 +20226,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1165.51</v>
+        <v>3225.26</v>
       </c>
     </row>
     <row r="307">
@@ -20661,7 +20661,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>3858-140-CM26</t>
+          <t>3858-141-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20701,32 +20701,28 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.722-9</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1793.56</v>
+        <v>920.83</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>3858-141-CM26</t>
+          <t>3858-140-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20766,22 +20762,26 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>920.83</v>
+        <v>1793.56</v>
       </c>
     </row>
     <row r="315">
@@ -21242,7 +21242,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3858-162-CM26</t>
+          <t>3858-163-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21282,28 +21282,32 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K322" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>1467.88</v>
+        <v>1983.89</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>3858-163-CM26</t>
+          <t>3858-162-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21343,26 +21347,22 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.722-9</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>1983.89</v>
+        <v>1467.88</v>
       </c>
     </row>
     <row r="324">
@@ -21433,7 +21433,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2258-2940-CM26</t>
+          <t>1410-302-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21473,17 +21473,17 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -21492,13 +21492,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>3675.44</v>
+        <v>779.65</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1410-302-CM26</t>
+          <t>2258-2940-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21523,12 +21523,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21538,17 +21538,17 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>779.65</v>
+        <v>3675.44</v>
       </c>
     </row>
     <row r="327">
@@ -21758,7 +21758,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>707415-56-CM26</t>
+          <t>1425773-38-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21783,12 +21783,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>88.951.800-6</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21798,17 +21798,17 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -21817,13 +21817,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>4824.44</v>
+        <v>1563.82</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1425773-38-CM26</t>
+          <t>707415-56-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21848,12 +21848,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>88.951.800-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21863,17 +21863,17 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -21882,7 +21882,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>1563.82</v>
+        <v>4824.44</v>
       </c>
     </row>
     <row r="332">
@@ -22018,7 +22018,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2258-3439-CM26</t>
+          <t>3845-32-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22038,17 +22038,17 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -22058,12 +22058,12 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>915.52</v>
+        <v>9527.610000000001</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>3845-32-CM26</t>
+          <t>2258-3439-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -22103,17 +22103,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -22123,12 +22123,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -22142,13 +22142,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>9527.610000000001</v>
+        <v>915.52</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>778992-108-CM26</t>
+          <t>778992-97-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22188,17 +22188,17 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -22207,13 +22207,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>4505.74</v>
+        <v>1079.12</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>778992-97-CM26</t>
+          <t>2258-3440-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22238,12 +22238,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22253,32 +22253,28 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.722-9</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1079.12</v>
+        <v>1186.03</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2258-3440-CM26</t>
+          <t>778992-108-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22303,12 +22299,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22318,22 +22314,26 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1186.03</v>
+        <v>4505.74</v>
       </c>
     </row>
     <row r="339">
@@ -22664,7 +22664,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2258-4177-CM26</t>
+          <t>2258-4176-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22704,32 +22704,28 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>7307.39</v>
+        <v>2118.78</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2258-4176-CM26</t>
+          <t>2258-4177-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22769,28 +22765,32 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>2118.78</v>
+        <v>7307.39</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>3834-143-CM26</t>
+          <t>3858-241-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22830,17 +22830,17 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>COMERCIAL VALLE SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>77.988.165-2</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -22849,13 +22849,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>851.13</v>
+        <v>806.63</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>930-87-CM26</t>
+          <t>3834-143-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22875,17 +22875,17 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22895,17 +22895,17 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL VALLE SPA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.988.165-2</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -22914,13 +22914,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1254.86</v>
+        <v>851.13</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>3858-241-CM26</t>
+          <t>930-87-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22940,17 +22940,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -22979,7 +22979,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>806.63</v>
+        <v>1254.86</v>
       </c>
     </row>
     <row r="349">
@@ -23180,7 +23180,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1697-149-CM26</t>
+          <t>2385-399-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23200,17 +23200,17 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -23239,13 +23239,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2962.14</v>
+        <v>14517.5</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2385-399-CM26</t>
+          <t>1697-149-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23265,17 +23265,17 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -23285,12 +23285,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -23304,7 +23304,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>14517.5</v>
+        <v>2962.14</v>
       </c>
     </row>
     <row r="354">
@@ -23440,7 +23440,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>769-400-CM26</t>
+          <t>3391-381-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23465,12 +23465,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23480,17 +23480,17 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -23499,7 +23499,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>7727.42</v>
+        <v>3186.08</v>
       </c>
     </row>
     <row r="357">
@@ -23570,7 +23570,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>3391-381-CM26</t>
+          <t>769-400-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23595,12 +23595,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23610,17 +23610,17 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -23629,7 +23629,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>3186.08</v>
+        <v>7727.42</v>
       </c>
     </row>
     <row r="359">
@@ -23700,7 +23700,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>930-105-CM26</t>
+          <t>1057384-508-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23725,12 +23725,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23740,17 +23740,17 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -23759,13 +23759,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>811.53</v>
+        <v>2346.5</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1057384-508-CM26</t>
+          <t>930-105-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23790,12 +23790,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23805,17 +23805,17 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -23824,7 +23824,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>2346.5</v>
+        <v>811.53</v>
       </c>
     </row>
     <row r="362">
@@ -24025,7 +24025,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>664-32-CM26</t>
+          <t>1573-28-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -24050,12 +24050,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>61.402.017-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -24065,17 +24065,17 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -24084,13 +24084,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>883.1</v>
+        <v>2518.24</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1573-28-CM26</t>
+          <t>664-32-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24115,12 +24115,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.402.017-2</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24130,17 +24130,17 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -24149,7 +24149,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>2518.24</v>
+        <v>883.1</v>
       </c>
     </row>
     <row r="367">
@@ -24805,7 +24805,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1233623-389-CM26</t>
+          <t>3858-338-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -24830,12 +24830,12 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -24864,13 +24864,13 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>23150.66</v>
+        <v>1351.86</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>3858-338-CM26</t>
+          <t>1233623-389-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -24929,7 +24929,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1351.86</v>
+        <v>23150.66</v>
       </c>
     </row>
     <row r="379">
@@ -25195,7 +25195,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>993-170-CM26</t>
+          <t>1233623-490-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25220,12 +25220,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -25235,17 +25235,17 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -25254,13 +25254,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>811.91</v>
+        <v>5440.62</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1233623-490-CM26</t>
+          <t>993-170-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25285,12 +25285,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25300,17 +25300,17 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -25319,7 +25319,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>5440.62</v>
+        <v>811.91</v>
       </c>
     </row>
     <row r="385">
@@ -25390,7 +25390,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1233623-453-CM26</t>
+          <t>1233623-502-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25449,13 +25449,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>4269.32</v>
+        <v>2897.75</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1233623-502-CM26</t>
+          <t>650-94-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25475,17 +25475,17 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25514,13 +25514,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2897.75</v>
+        <v>2201.44</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1697-221-CM26</t>
+          <t>1233623-453-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25545,12 +25545,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25560,12 +25560,12 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
@@ -25579,13 +25579,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>4785.88</v>
+        <v>4269.32</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>650-94-CM26</t>
+          <t>1697-221-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25605,17 +25605,17 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25625,12 +25625,12 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>2201.44</v>
+        <v>4785.88</v>
       </c>
     </row>
     <row r="390">
@@ -25975,7 +25975,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>769-604-CM26</t>
+          <t>2258-6908-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -26000,12 +26000,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -26015,12 +26015,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -26034,13 +26034,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>3126.27</v>
+        <v>3664.21</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2258-6908-CM26</t>
+          <t>769-604-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -26065,12 +26065,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -26080,12 +26080,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -26099,7 +26099,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>3664.21</v>
+        <v>3126.27</v>
       </c>
     </row>
     <row r="397">
@@ -26255,7 +26255,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -26320,7 +26320,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -26430,7 +26430,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>4999-46-CM26</t>
+          <t>4999-47-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -26470,12 +26470,12 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -26489,13 +26489,13 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>3245.73</v>
+        <v>1373.38</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1233623-676-CM26</t>
+          <t>4999-46-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -26535,12 +26535,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -26554,13 +26554,13 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>11445.21</v>
+        <v>3245.73</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1261592-1169-CM26</t>
+          <t>1233623-676-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26575,22 +26575,22 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -26600,17 +26600,17 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -26619,13 +26619,13 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>7444.51</v>
+        <v>11445.21</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1233623-673-CM26</t>
+          <t>1261592-1169-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -26640,7 +26640,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -26650,12 +26650,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -26665,17 +26665,17 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -26684,13 +26684,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>11609.76</v>
+        <v>7444.51</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1233623-607-CM26</t>
+          <t>1233623-673-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26710,7 +26710,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -26749,13 +26749,13 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>3677.64</v>
+        <v>11609.76</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>697036-66-CM26</t>
+          <t>1233623-607-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26770,22 +26770,22 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26814,13 +26814,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2329.1</v>
+        <v>3677.64</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1057385-343-CM26</t>
+          <t>697036-66-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26835,22 +26835,22 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26879,13 +26879,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>1415.49</v>
+        <v>2329.1</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1233623-752-CM26</t>
+          <t>1057385-343-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26900,22 +26900,22 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -26944,7 +26944,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>16945.52</v>
+        <v>1415.49</v>
       </c>
     </row>
     <row r="410">
@@ -27015,7 +27015,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1233623-706-CM26</t>
+          <t>1233623-752-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -27030,7 +27030,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -27074,7 +27074,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>16481.24</v>
+        <v>16945.52</v>
       </c>
     </row>
     <row r="412">
@@ -27145,7 +27145,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1233623-763-CM26</t>
+          <t>1233623-706-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27160,12 +27160,12 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>4724.86</v>
+        <v>16481.24</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>3858-425-CM26</t>
+          <t>1233623-763-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27225,7 +27225,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -27235,12 +27235,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -27269,72 +27269,787 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>751.9299999999999</v>
+        <v>4724.86</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
+          <t>1057385-358-CM26</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>61.606.204-2</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M415" s="2" t="n">
+        <v>822.48</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>3858-425-CM26</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M416" s="2" t="n">
+        <v>751.9299999999999</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
           <t>3391-573-CM26</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>2239-16-LR24</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr">
+      <c r="D417" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr">
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>61.101.086-9</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M417" s="2" t="n">
+        <v>2571.59</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2215-1098-CM26</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>61.101.086-9</t>
-        </is>
-      </c>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
-        </is>
-      </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I415" t="inlineStr">
-        <is>
-          <t>DIMERC S A</t>
-        </is>
-      </c>
-      <c r="J415" t="inlineStr">
-        <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K415" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="L415" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M415" s="2" t="n">
-        <v>2571.59</v>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>61.606.202-6</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M418" s="2" t="n">
+        <v>14231.39</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>1233623-819-CM26</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M419" s="2" t="n">
+        <v>32752.16</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>1233623-846-CM26</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M420" s="2" t="n">
+        <v>6997.89</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>707415-110-CM26</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M421" s="2" t="n">
+        <v>3064.44</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>1233623-893-CM26</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M422" s="2" t="n">
+        <v>9723.139999999999</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>1057384-807-CM26</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>61.606.203-4</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M423" s="2" t="n">
+        <v>3069.23</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>707415-113-CM26</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M424" s="2" t="n">
+        <v>742.14</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>1233623-925-CM26</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M425" s="2" t="n">
+        <v>2772.43</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2258-8185-CM26</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M426" s="2" t="n">
+        <v>12616.08</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/antofagasta.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M426"/>
+  <dimension ref="A1:M427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -18146,7 +18146,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -18516,7 +18516,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2215-174-CM26</t>
+          <t>3174-18-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -18541,12 +18541,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.102.045-7</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18556,17 +18556,17 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -18575,7 +18575,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>36800.31</v>
+        <v>1013.59</v>
       </c>
     </row>
     <row r="281">
@@ -18646,7 +18646,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>3149-54-CM26</t>
+          <t>2215-174-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18671,12 +18671,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18705,13 +18705,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>32732.68</v>
+        <v>36800.31</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>558869-26-CM26</t>
+          <t>3149-54-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18726,22 +18726,22 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18751,17 +18751,17 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -18770,13 +18770,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>33393.3</v>
+        <v>32732.68</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>3858-85-CM26</t>
+          <t>558869-26-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -18801,12 +18801,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18816,17 +18816,17 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -18835,13 +18835,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>909.8099999999999</v>
+        <v>33393.3</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>3858-84-CM26</t>
+          <t>3858-85-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18881,17 +18881,17 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -18900,13 +18900,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>1205.72</v>
+        <v>909.8099999999999</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>558869-28-CM26</t>
+          <t>3858-84-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18931,12 +18931,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18946,17 +18946,17 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -18965,13 +18965,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>6742.58</v>
+        <v>1205.72</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2122-31-CM26</t>
+          <t>558869-28-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18991,17 +18991,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19011,17 +19011,17 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -19030,13 +19030,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1026.2</v>
+        <v>6742.58</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>707415-22-CM26</t>
+          <t>2122-31-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19056,17 +19056,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19095,13 +19095,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1061.33</v>
+        <v>1026.2</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>707415-21-CM26</t>
+          <t>707415-22-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19160,13 +19160,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1082.03</v>
+        <v>1061.33</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1410-146-CM26</t>
+          <t>707415-21-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19176,27 +19176,27 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -19206,17 +19206,17 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -19225,13 +19225,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>889.6</v>
+        <v>1082.03</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1233623-48-CM26</t>
+          <t>1410-146-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -19256,12 +19256,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19271,17 +19271,17 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -19290,13 +19290,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2723.26</v>
+        <v>889.6</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>3391-159-CM26</t>
+          <t>1233623-48-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19321,12 +19321,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19355,13 +19355,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>3292.02</v>
+        <v>2723.26</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>3391-158-CM26</t>
+          <t>3391-159-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19401,17 +19401,17 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -19420,13 +19420,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2507.57</v>
+        <v>3292.02</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1079454-56-CM26</t>
+          <t>3391-158-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19441,7 +19441,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -19451,12 +19451,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19466,17 +19466,17 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -19485,13 +19485,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>8411.860000000001</v>
+        <v>2507.57</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>3858-97-CM26</t>
+          <t>1079454-56-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19506,22 +19506,22 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19531,17 +19531,17 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -19550,13 +19550,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>4843.42</v>
+        <v>8411.860000000001</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>3858-99-CM26</t>
+          <t>3858-98-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19596,17 +19596,17 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>OPEN SANTIAGO SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>78.069.505-6</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -19615,13 +19615,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1779.26</v>
+        <v>3927.25</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3858-98-CM26</t>
+          <t>3858-99-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19661,17 +19661,17 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>OPEN SANTIAGO SPA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.069.505-6</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -19680,13 +19680,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>3927.25</v>
+        <v>1779.26</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>769-136-CM26</t>
+          <t>3858-97-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19701,22 +19701,22 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19726,12 +19726,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -19745,13 +19745,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>34581.68</v>
+        <v>4843.42</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3845-14-CM26</t>
+          <t>769-136-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19771,17 +19771,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19791,17 +19791,17 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -19810,13 +19810,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2529.01</v>
+        <v>34581.68</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1346284-56-CM26</t>
+          <t>3845-14-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19831,22 +19831,22 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19856,17 +19856,17 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -19875,7 +19875,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>856.27</v>
+        <v>2529.01</v>
       </c>
     </row>
     <row r="301">
@@ -19946,7 +19946,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1057385-66-CM26</t>
+          <t>1346284-56-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19961,7 +19961,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -19971,12 +19971,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19986,17 +19986,17 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -20005,13 +20005,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>924.26</v>
+        <v>856.27</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>4291-180-CM26</t>
+          <t>1057385-66-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -20026,22 +20026,22 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -20051,17 +20051,17 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -20070,13 +20070,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1401.7</v>
+        <v>924.26</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>697036-11-CM26</t>
+          <t>4291-180-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20091,7 +20091,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -20101,12 +20101,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -20135,13 +20135,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1165.51</v>
+        <v>1401.7</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1079454-67-CM26</t>
+          <t>697036-11-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20161,17 +20161,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20181,17 +20181,17 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -20200,13 +20200,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>20250.67</v>
+        <v>1165.51</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>778998-15-CM26</t>
+          <t>1079454-67-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20231,12 +20231,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20246,17 +20246,17 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -20265,13 +20265,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>3225.26</v>
+        <v>20250.67</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>4617-7-CM26</t>
+          <t>778998-15-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20286,7 +20286,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -20296,12 +20296,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20330,13 +20330,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>2168.99</v>
+        <v>3225.26</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1077908-54-CM26</t>
+          <t>4617-7-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20351,7 +20351,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -20361,12 +20361,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20395,13 +20395,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>3668.42</v>
+        <v>2168.99</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1410-236-CM26</t>
+          <t>1077908-54-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20416,7 +20416,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -20426,12 +20426,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20441,12 +20441,12 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -20460,13 +20460,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>4328.97</v>
+        <v>3668.42</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>778998-22-CM26</t>
+          <t>1410-236-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20481,7 +20481,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -20491,12 +20491,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.067.906-9</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -20525,13 +20525,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>1849.86</v>
+        <v>4328.97</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>712-11-CM26</t>
+          <t>778998-22-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20546,7 +20546,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -20556,12 +20556,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -20590,13 +20590,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>1083.16</v>
+        <v>1849.86</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2258-2613-CM26</t>
+          <t>712-11-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20611,7 +20611,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -20621,12 +20621,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20636,17 +20636,17 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -20655,13 +20655,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>16655.55</v>
+        <v>1083.16</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>3858-141-CM26</t>
+          <t>2258-2613-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20671,27 +20671,27 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20701,28 +20701,32 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr"/>
+          <t>76.213.681-3</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>920.83</v>
+        <v>16655.55</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>3858-140-CM26</t>
+          <t>3858-141-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20762,32 +20766,28 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.722-9</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>1793.56</v>
+        <v>920.83</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>3858-147-CM26</t>
+          <t>3858-140-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -20846,13 +20846,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>764.9400000000001</v>
+        <v>1793.56</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>3858-158-CM26</t>
+          <t>3858-147-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -20892,17 +20892,17 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -20911,13 +20911,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>770.64</v>
+        <v>764.9400000000001</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>3858-159-CM26</t>
+          <t>3858-158-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20957,17 +20957,17 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -20976,13 +20976,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>791.12</v>
+        <v>770.64</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1077908-64-CM26</t>
+          <t>3858-159-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -21002,17 +21002,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -21022,17 +21022,17 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -21041,13 +21041,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1596.2</v>
+        <v>791.12</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>662457-6-CM26</t>
+          <t>1077908-64-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -21072,12 +21072,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -21087,17 +21087,17 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -21106,13 +21106,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>823.5</v>
+        <v>1596.2</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1220203-27-CM26</t>
+          <t>662457-6-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -21137,12 +21137,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -21152,17 +21152,17 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -21171,13 +21171,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>889.5599999999999</v>
+        <v>823.5</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>548850-34-CM26</t>
+          <t>1220203-27-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21192,7 +21192,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -21202,12 +21202,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -21217,17 +21217,17 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -21236,13 +21236,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1604.44</v>
+        <v>889.5599999999999</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3858-163-CM26</t>
+          <t>548850-34-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21262,17 +21262,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -21282,17 +21282,17 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -21301,13 +21301,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>1983.89</v>
+        <v>1604.44</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>3858-162-CM26</t>
+          <t>3858-163-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21347,28 +21347,32 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>1467.88</v>
+        <v>1983.89</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1410-292-CM26</t>
+          <t>3858-162-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -21388,17 +21392,17 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -21408,32 +21412,28 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.722-9</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1347.98</v>
+        <v>1467.88</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1410-302-CM26</t>
+          <t>1410-292-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -21492,13 +21492,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>779.65</v>
+        <v>1347.98</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2258-2940-CM26</t>
+          <t>1410-302-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21523,12 +21523,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21538,17 +21538,17 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -21557,13 +21557,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>3675.44</v>
+        <v>779.65</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1220203-32-CM26</t>
+          <t>2258-2940-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -21588,12 +21588,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21603,17 +21603,17 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -21622,13 +21622,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1024.92</v>
+        <v>3675.44</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1354-11-CM26</t>
+          <t>1220203-32-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21643,7 +21643,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -21653,12 +21653,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.002.008-9</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21668,17 +21668,17 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -21687,13 +21687,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>18037.86</v>
+        <v>1024.92</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1057385-114-CM26</t>
+          <t>1354-11-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21708,7 +21708,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -21718,12 +21718,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.002.008-9</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21733,17 +21733,17 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -21752,13 +21752,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1456.07</v>
+        <v>18037.86</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1425773-38-CM26</t>
+          <t>1057385-114-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21773,22 +21773,22 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>88.951.800-6</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21817,13 +21817,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1563.82</v>
+        <v>1456.07</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>707415-56-CM26</t>
+          <t>1425773-38-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21848,12 +21848,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>88.951.800-6</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21863,17 +21863,17 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -21882,13 +21882,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>4824.44</v>
+        <v>1563.82</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1057385-120-CM26</t>
+          <t>707415-56-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21903,22 +21903,22 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -21947,13 +21947,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>877.12</v>
+        <v>4824.44</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1346284-91-CM26</t>
+          <t>1057385-120-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21963,12 +21963,12 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21993,17 +21993,17 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -22012,13 +22012,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>817.71</v>
+        <v>877.12</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>3845-32-CM26</t>
+          <t>1346284-91-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22033,22 +22033,22 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -22058,17 +22058,17 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>9527.610000000001</v>
+        <v>817.71</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2258-3439-CM26</t>
+          <t>3845-32-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -22103,17 +22103,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -22123,12 +22123,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -22142,13 +22142,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>915.52</v>
+        <v>9527.610000000001</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>778992-97-CM26</t>
+          <t>2258-3439-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -22173,12 +22173,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -22188,12 +22188,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -22207,13 +22207,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>1079.12</v>
+        <v>915.52</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2258-3440-CM26</t>
+          <t>778992-97-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22238,12 +22238,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22253,22 +22253,26 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1186.03</v>
+        <v>1079.12</v>
       </c>
     </row>
     <row r="338">
@@ -22339,7 +22343,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>4291-472-CM26</t>
+          <t>2258-3440-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22354,22 +22358,22 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -22379,32 +22383,28 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.722-9</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>2455.23</v>
+        <v>1186.03</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2429-506-CM26</t>
+          <t>4291-472-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22419,22 +22419,22 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -22444,17 +22444,17 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -22463,13 +22463,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1146.59</v>
+        <v>2455.23</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>558869-57-CM26</t>
+          <t>2429-506-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22484,22 +22484,22 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22509,17 +22509,17 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -22528,13 +22528,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>290038.33</v>
+        <v>1146.59</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>4468-64-CM26</t>
+          <t>558869-57-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22549,7 +22549,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -22559,12 +22559,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22574,17 +22574,17 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -22593,7 +22593,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>10060.57</v>
+        <v>290038.33</v>
       </c>
     </row>
     <row r="343">
@@ -22664,7 +22664,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2258-4176-CM26</t>
+          <t>4468-64-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22679,7 +22679,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -22689,12 +22689,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22704,28 +22704,32 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2118.78</v>
+        <v>10060.57</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2258-4177-CM26</t>
+          <t>2258-4176-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22765,32 +22769,28 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>7307.39</v>
+        <v>2118.78</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>3858-241-CM26</t>
+          <t>2258-4177-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22805,22 +22805,22 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -22830,17 +22830,17 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -22849,13 +22849,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>806.63</v>
+        <v>7307.39</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>3834-143-CM26</t>
+          <t>3858-241-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22895,17 +22895,17 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>COMERCIAL VALLE SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>77.988.165-2</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -22914,13 +22914,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>851.13</v>
+        <v>806.63</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>930-87-CM26</t>
+          <t>3834-143-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22940,17 +22940,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -22960,17 +22960,17 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL VALLE SPA</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.988.165-2</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -22979,13 +22979,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1254.86</v>
+        <v>851.13</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>707415-66-CM26</t>
+          <t>930-87-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -23000,22 +23000,22 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -23025,17 +23025,17 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -23044,13 +23044,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>968.17</v>
+        <v>1254.86</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>3858-249-CM26</t>
+          <t>707415-66-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -23060,12 +23060,12 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -23075,12 +23075,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -23109,13 +23109,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>7583.85</v>
+        <v>968.17</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1233623-244-CM26</t>
+          <t>3858-249-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -23140,12 +23140,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -23174,13 +23174,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>13252.42</v>
+        <v>7583.85</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2385-399-CM26</t>
+          <t>1233623-244-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23195,7 +23195,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -23205,12 +23205,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -23239,13 +23239,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>14517.5</v>
+        <v>13252.42</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1697-149-CM26</t>
+          <t>2385-399-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23265,17 +23265,17 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -23285,12 +23285,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -23304,13 +23304,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2962.14</v>
+        <v>14517.5</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1253-7-CM26</t>
+          <t>1697-149-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -23325,7 +23325,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -23335,12 +23335,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>60.805.055-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -23350,17 +23350,17 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -23369,13 +23369,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>910.8099999999999</v>
+        <v>2962.14</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2215-673-CM26</t>
+          <t>1253-7-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23390,7 +23390,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -23400,12 +23400,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>60.805.055-8</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23415,17 +23415,17 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -23434,13 +23434,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>4300.46</v>
+        <v>910.8099999999999</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>3391-381-CM26</t>
+          <t>2215-673-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23455,7 +23455,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -23465,12 +23465,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23480,17 +23480,17 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -23499,13 +23499,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>3186.08</v>
+        <v>4300.46</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>769-401-CM26</t>
+          <t>3391-381-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23530,12 +23530,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23545,17 +23545,17 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -23564,13 +23564,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>10916.98</v>
+        <v>3186.08</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>769-400-CM26</t>
+          <t>769-401-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23629,13 +23629,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>7727.42</v>
+        <v>10916.98</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>930-104-CM26</t>
+          <t>769-400-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -23660,12 +23660,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23675,17 +23675,17 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -23694,13 +23694,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1115.01</v>
+        <v>7727.42</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1057384-508-CM26</t>
+          <t>930-104-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23725,12 +23725,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23740,17 +23740,17 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -23759,13 +23759,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2346.5</v>
+        <v>1115.01</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>930-105-CM26</t>
+          <t>1057384-508-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23790,12 +23790,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23805,17 +23805,17 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -23824,13 +23824,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>811.53</v>
+        <v>2346.5</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1410-543-CM26</t>
+          <t>930-105-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23845,7 +23845,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -23855,12 +23855,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23870,17 +23870,17 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>78.067.906-9</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -23889,13 +23889,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1174.89</v>
+        <v>811.53</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1233623-309-CM26</t>
+          <t>1410-543-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23910,22 +23910,22 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -23935,12 +23935,12 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS Y SUMINISTROS ST SPA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.067.906-9</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
@@ -23954,13 +23954,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>8464.120000000001</v>
+        <v>1174.89</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1573-27-CM26</t>
+          <t>1233623-309-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23980,17 +23980,17 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -24000,17 +24000,17 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -24019,13 +24019,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>33145.34</v>
+        <v>8464.120000000001</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1573-28-CM26</t>
+          <t>1573-27-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -24084,13 +24084,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>2518.24</v>
+        <v>33145.34</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>664-32-CM26</t>
+          <t>1573-28-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24115,12 +24115,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>61.402.017-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24130,17 +24130,17 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -24149,13 +24149,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>883.1</v>
+        <v>2518.24</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2258-5255-CM26</t>
+          <t>664-32-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24170,7 +24170,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -24180,12 +24180,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.402.017-2</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24195,17 +24195,17 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -24214,13 +24214,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1579.52</v>
+        <v>883.1</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2258-5485-CM26</t>
+          <t>2258-5255-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24230,12 +24230,12 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -24260,17 +24260,17 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -24279,13 +24279,13 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>781.97</v>
+        <v>1579.52</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>4617-13-CM26</t>
+          <t>2258-5485-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24310,12 +24310,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -24325,12 +24325,12 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
@@ -24344,13 +24344,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>2169.21</v>
+        <v>781.97</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>778992-188-CM26</t>
+          <t>4617-13-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24365,7 +24365,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -24375,12 +24375,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -24390,17 +24390,17 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -24409,13 +24409,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1235.27</v>
+        <v>2169.21</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2258-5199-CM26</t>
+          <t>778992-188-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24430,7 +24430,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -24440,12 +24440,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -24455,17 +24455,17 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -24474,13 +24474,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>7978.61</v>
+        <v>1235.27</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2122-140-CM26</t>
+          <t>2258-5199-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24495,7 +24495,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -24505,12 +24505,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -24520,17 +24520,17 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -24539,13 +24539,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1265.46</v>
+        <v>7978.61</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>707415-84-CM26</t>
+          <t>2122-140-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24560,22 +24560,22 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24585,17 +24585,17 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -24604,13 +24604,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>3992.23</v>
+        <v>1265.46</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1077908-129-CM26</t>
+          <t>707415-84-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24625,7 +24625,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -24635,12 +24635,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24669,13 +24669,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>4244.46</v>
+        <v>3992.23</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1261592-898-CM26</t>
+          <t>1077908-129-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -24700,12 +24700,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24715,17 +24715,17 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -24734,13 +24734,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>904.22</v>
+        <v>4244.46</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1077908-134-CM26</t>
+          <t>1261592-898-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -24765,12 +24765,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -24780,17 +24780,17 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -24799,13 +24799,13 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>1012.22</v>
+        <v>904.22</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>3858-338-CM26</t>
+          <t>1077908-134-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -24820,22 +24820,22 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -24845,17 +24845,17 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -24864,13 +24864,13 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>1351.86</v>
+        <v>1012.22</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1233623-389-CM26</t>
+          <t>3858-338-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24890,17 +24890,17 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -24929,13 +24929,13 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>23150.66</v>
+        <v>1351.86</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1233623-401-CM26</t>
+          <t>1233623-389-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -24950,7 +24950,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -24994,13 +24994,13 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>3650.78</v>
+        <v>23150.66</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1346284-145-CM26</t>
+          <t>1233623-401-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -25010,27 +25010,27 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -25040,17 +25040,17 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -25059,13 +25059,13 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>906.91</v>
+        <v>3650.78</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1346284-148-CM26</t>
+          <t>1346284-145-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -25080,7 +25080,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -25124,13 +25124,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>1725.26</v>
+        <v>906.91</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1410-728-CM26</t>
+          <t>1346284-148-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -25155,12 +25155,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -25189,13 +25189,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>796.6900000000001</v>
+        <v>1725.26</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1233623-490-CM26</t>
+          <t>1410-728-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25210,22 +25210,22 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -25235,17 +25235,17 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -25254,13 +25254,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>5440.62</v>
+        <v>796.6900000000001</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>993-170-CM26</t>
+          <t>1233623-490-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25280,17 +25280,17 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25300,17 +25300,17 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -25319,13 +25319,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>811.91</v>
+        <v>5440.62</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>707415-94-CM26</t>
+          <t>993-170-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25350,12 +25350,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25365,17 +25365,17 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -25384,13 +25384,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1108.56</v>
+        <v>811.91</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1233623-502-CM26</t>
+          <t>707415-94-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -25415,12 +25415,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25449,13 +25449,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>2897.75</v>
+        <v>1108.56</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>650-94-CM26</t>
+          <t>1233623-502-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25475,17 +25475,17 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25514,13 +25514,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2201.44</v>
+        <v>2897.75</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1233623-453-CM26</t>
+          <t>650-94-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25540,17 +25540,17 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25579,13 +25579,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>4269.32</v>
+        <v>2201.44</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1697-221-CM26</t>
+          <t>1233623-453-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25610,12 +25610,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25625,12 +25625,12 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -25644,13 +25644,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>4785.88</v>
+        <v>4269.32</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1410-789-CM26</t>
+          <t>1697-221-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25665,22 +25665,22 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25690,17 +25690,17 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -25709,13 +25709,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>1224.21</v>
+        <v>4785.88</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1233623-492-CM26</t>
+          <t>1410-789-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25730,22 +25730,22 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25755,17 +25755,17 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -25774,13 +25774,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>34033.98</v>
+        <v>1224.21</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1033-53-CM26</t>
+          <t>1233623-492-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25800,17 +25800,17 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25839,13 +25839,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>791.8099999999999</v>
+        <v>34033.98</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>778992-221-CM26</t>
+          <t>1033-53-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25860,7 +25860,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -25870,12 +25870,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -25885,12 +25885,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -25904,13 +25904,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>1560.68</v>
+        <v>791.8099999999999</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1233623-533-CM26</t>
+          <t>778992-221-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25930,17 +25930,17 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -25950,12 +25950,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -25969,13 +25969,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>12678.07</v>
+        <v>1560.68</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2258-6908-CM26</t>
+          <t>1233623-533-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -26000,12 +26000,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -26034,13 +26034,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>3664.21</v>
+        <v>12678.07</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>769-604-CM26</t>
+          <t>2258-6908-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -26065,12 +26065,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -26080,12 +26080,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -26099,13 +26099,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>3126.27</v>
+        <v>3664.21</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2258-6907-CM26</t>
+          <t>769-604-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -26130,12 +26130,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -26145,12 +26145,12 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -26164,13 +26164,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>4475.76</v>
+        <v>3126.27</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1013609-113-CM26</t>
+          <t>2258-6907-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26185,7 +26185,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -26195,12 +26195,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>65.158.175-3</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26210,17 +26210,17 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -26229,13 +26229,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>982.76</v>
+        <v>4475.76</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1233623-608-CM26</t>
+          <t>1013609-113-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26245,12 +26245,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -26260,12 +26260,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>65.158.175-3</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -26275,17 +26275,17 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
@@ -26294,13 +26294,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1982.02</v>
+        <v>982.76</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1057385-310-CM26</t>
+          <t>1233623-608-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -26315,7 +26315,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -26325,12 +26325,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -26340,12 +26340,12 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -26359,13 +26359,13 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>1165.41</v>
+        <v>1982.02</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>1220203-95-CM26</t>
+          <t>1057385-310-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -26380,7 +26380,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -26390,12 +26390,12 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -26405,12 +26405,12 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
@@ -26424,13 +26424,13 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1471.64</v>
+        <v>1165.41</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>4999-47-CM26</t>
+          <t>1220203-95-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -26445,22 +26445,22 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -26489,13 +26489,13 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>1373.38</v>
+        <v>1471.64</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>4999-46-CM26</t>
+          <t>4999-47-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -26535,12 +26535,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -26554,13 +26554,13 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>3245.73</v>
+        <v>1373.38</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1233623-676-CM26</t>
+          <t>4999-46-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26575,7 +26575,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -26585,12 +26585,12 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -26600,12 +26600,12 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -26619,13 +26619,13 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>11445.21</v>
+        <v>3245.73</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1261592-1169-CM26</t>
+          <t>1233623-676-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -26640,22 +26640,22 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -26665,17 +26665,17 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -26684,13 +26684,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>7444.51</v>
+        <v>11445.21</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1233623-673-CM26</t>
+          <t>1261592-1169-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26705,7 +26705,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -26715,12 +26715,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -26730,17 +26730,17 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -26749,13 +26749,13 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>11609.76</v>
+        <v>7444.51</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1233623-607-CM26</t>
+          <t>1233623-673-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26814,13 +26814,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>3677.64</v>
+        <v>11609.76</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>697036-66-CM26</t>
+          <t>1233623-607-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26835,22 +26835,22 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26879,13 +26879,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>2329.1</v>
+        <v>3677.64</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1057385-343-CM26</t>
+          <t>697036-66-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26900,22 +26900,22 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -26944,13 +26944,13 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1415.49</v>
+        <v>2329.1</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>3916-386-CM26</t>
+          <t>1057385-343-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -26965,22 +26965,22 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26990,17 +26990,17 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -27009,13 +27009,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>3014.78</v>
+        <v>1415.49</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1233623-752-CM26</t>
+          <t>3916-386-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -27040,12 +27040,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -27055,17 +27055,17 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -27074,13 +27074,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>16945.52</v>
+        <v>3014.78</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1410-888-CM26</t>
+          <t>1233623-752-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -27095,22 +27095,22 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -27120,12 +27120,12 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -27139,13 +27139,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1043.97</v>
+        <v>16945.52</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1233623-706-CM26</t>
+          <t>1410-888-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27185,12 +27185,12 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>16481.24</v>
+        <v>1043.97</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1233623-763-CM26</t>
+          <t>1233623-706-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27225,12 +27225,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -27269,13 +27269,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>4724.86</v>
+        <v>16481.24</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1057385-358-CM26</t>
+          <t>1233623-763-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27290,7 +27290,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -27300,12 +27300,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -27315,17 +27315,17 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
@@ -27334,13 +27334,13 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>822.48</v>
+        <v>4724.86</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>3858-425-CM26</t>
+          <t>1057385-358-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27355,22 +27355,22 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -27380,17 +27380,17 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
@@ -27399,13 +27399,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>751.9299999999999</v>
+        <v>822.48</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>3391-573-CM26</t>
+          <t>3858-425-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27420,7 +27420,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -27430,12 +27430,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -27445,17 +27445,17 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -27464,13 +27464,13 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>2571.59</v>
+        <v>751.9299999999999</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2215-1098-CM26</t>
+          <t>3391-573-CM26</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -27480,27 +27480,27 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -27510,17 +27510,17 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
@@ -27529,13 +27529,13 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>14231.39</v>
+        <v>2571.59</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>1233623-819-CM26</t>
+          <t>2215-1098-CM26</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -27550,7 +27550,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -27560,12 +27560,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -27575,17 +27575,17 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
@@ -27594,13 +27594,13 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>32752.16</v>
+        <v>14231.39</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>1233623-846-CM26</t>
+          <t>1233623-819-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27615,7 +27615,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -27659,13 +27659,13 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>6997.89</v>
+        <v>32752.16</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>707415-110-CM26</t>
+          <t>1233623-846-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27680,7 +27680,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -27690,12 +27690,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -27724,13 +27724,13 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>3064.44</v>
+        <v>6997.89</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>1233623-893-CM26</t>
+          <t>707415-110-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -27745,7 +27745,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -27755,12 +27755,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -27789,13 +27789,13 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>9723.139999999999</v>
+        <v>3064.44</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>1057384-807-CM26</t>
+          <t>1233623-893-CM26</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -27810,7 +27810,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -27820,12 +27820,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -27854,13 +27854,13 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>3069.23</v>
+        <v>9723.139999999999</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>707415-113-CM26</t>
+          <t>1057384-807-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -27885,12 +27885,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -27919,13 +27919,13 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>742.14</v>
+        <v>3069.23</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1233623-925-CM26</t>
+          <t>707415-113-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -27940,7 +27940,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -27950,12 +27950,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -27984,71 +27984,136 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>2772.43</v>
+        <v>742.14</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
+          <t>1233623-925-CM26</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M426" s="2" t="n">
+        <v>2772.43</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
           <t>2258-8185-CM26</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>2239-16-LR24</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr">
+      <c r="D427" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E426" t="inlineStr">
+      <c r="E427" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F426" t="inlineStr">
+      <c r="F427" t="inlineStr">
         <is>
           <t>61.606.201-8</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr">
+      <c r="G427" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I426" t="inlineStr">
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
-      <c r="J426" t="inlineStr">
+      <c r="J427" t="inlineStr">
         <is>
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr">
+      <c r="K427" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L426" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M426" s="2" t="n">
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M427" s="2" t="n">
         <v>12616.08</v>
       </c>
     </row>
